--- a/wwwroot/assets/template/User_Template.xlsx
+++ b/wwwroot/assets/template/User_Template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASP.NET\WebTruyenTranh\wwwroot\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F56DD45-32A5-4951-87FF-720E0BD12AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -60,19 +61,19 @@
     <t>Nguyễn Van Hai</t>
   </si>
   <si>
-    <t>hai@gmail.com</t>
-  </si>
-  <si>
     <t>© Leningrad</t>
   </si>
   <si>
-    <t>giap@gmail.com</t>
+    <t>giaptest@gmail.com</t>
+  </si>
+  <si>
+    <t>haitest@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
   </numFmts>
@@ -164,6 +165,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -173,7 +175,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -454,53 +455,53 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="7" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" customWidth="1"/>
+    <col min="6" max="7" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-    </row>
-    <row r="4" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -520,15 +521,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="3">
         <v>46000</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>15</v>
+      <c r="C6" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="D6" s="2">
         <v>98765779</v>
@@ -540,15 +541,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="3">
         <v>36872</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>13</v>
+      <c r="C7" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="D7" s="2">
         <v>46556767</v>
@@ -560,16 +561,16 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -579,7 +580,8 @@
     <mergeCell ref="A9:G9"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C6" r:id="rId1"/>
+    <hyperlink ref="C6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C7" r:id="rId2" xr:uid="{90980F84-6D13-4840-A926-D865B7536B63}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/wwwroot/assets/template/User_Template.xlsx
+++ b/wwwroot/assets/template/User_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASP.NET\WebTruyenTranh\wwwroot\assets\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F56DD45-32A5-4951-87FF-720E0BD12AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE94BA0-035D-47CC-B2B0-EC0533D7A31A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,12 +25,6 @@
     <t>LIST OF USERS</t>
   </si>
   <si>
-    <t>Export date: 22/01/2026 17:00:46</t>
-  </si>
-  <si>
-    <t>Total users: 8</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -49,25 +43,31 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Nguyễn Văn Giap</t>
-  </si>
-  <si>
     <t>Male</t>
   </si>
   <si>
     <t>Active</t>
   </si>
   <si>
-    <t>Nguyễn Van Hai</t>
-  </si>
-  <si>
     <t>© Leningrad</t>
   </si>
   <si>
+    <t>Nguyen Van Giap</t>
+  </si>
+  <si>
+    <t>Nguyen Van Hai</t>
+  </si>
+  <si>
     <t>giaptest@gmail.com</t>
   </si>
   <si>
     <t>haitest@gmail.com</t>
+  </si>
+  <si>
+    <t>Total users: 2</t>
+  </si>
+  <si>
+    <t>Export date: 22/09/2026 17:00:46</t>
   </si>
 </sst>
 </file>
@@ -480,7 +480,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -491,7 +491,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -503,67 +503,67 @@
     <row r="4" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="3">
         <v>46000</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6" s="2">
         <v>98765779</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="3">
         <v>36872</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2">
         <v>46556767</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -581,7 +581,7 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C7" r:id="rId2" xr:uid="{90980F84-6D13-4840-A926-D865B7536B63}"/>
+    <hyperlink ref="C7" r:id="rId2" xr:uid="{ED93BC40-7E31-4847-8576-A39AACF019BE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
